--- a/ECB_stdev.xlsx
+++ b/ECB_stdev.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -130,13 +130,13 @@
         <v>5.7047338485717773</v>
       </c>
       <c r="C5" s="2">
-        <v>5.647674560546875</v>
+        <v>5.6514396667480469</v>
       </c>
       <c r="D5" s="2">
         <v>5.6991052627563477</v>
       </c>
       <c r="E5" s="2">
-        <v>5.6075396537780762</v>
+        <v>5.6050467491149902</v>
       </c>
     </row>
     <row r="6">
@@ -147,13 +147,13 @@
         <v>6.0612626075744629</v>
       </c>
       <c r="C6" s="2">
-        <v>5.9655489921569824</v>
+        <v>5.9633898735046387</v>
       </c>
       <c r="D6" s="2">
         <v>5.7083125114440918</v>
       </c>
       <c r="E6" s="2">
-        <v>5.6186976432800293</v>
+        <v>5.6166300773620605</v>
       </c>
     </row>
     <row r="7">
@@ -164,13 +164,13 @@
         <v>5.649012565612793</v>
       </c>
       <c r="C7" s="2">
-        <v>5.5414590835571289</v>
+        <v>5.5390996932983398</v>
       </c>
       <c r="D7" s="2">
         <v>5.6333155632019043</v>
       </c>
       <c r="E7" s="2">
-        <v>5.5496826171875</v>
+        <v>5.548466682434082</v>
       </c>
     </row>
     <row r="8">
@@ -181,13 +181,13 @@
         <v>5.9765419960021973</v>
       </c>
       <c r="C8" s="2">
-        <v>5.9174699783325195</v>
+        <v>5.9145746231079102</v>
       </c>
       <c r="D8" s="2">
         <v>5.6158556938171387</v>
       </c>
       <c r="E8" s="2">
-        <v>5.538426399230957</v>
+        <v>5.5377569198608398</v>
       </c>
     </row>
     <row r="9">
@@ -198,13 +198,13 @@
         <v>5.1039748191833496</v>
       </c>
       <c r="C9" s="2">
-        <v>4.9655461311340332</v>
+        <v>4.9567303657531738</v>
       </c>
       <c r="D9" s="2">
         <v>5.6924982070922852</v>
       </c>
       <c r="E9" s="2">
-        <v>5.6199564933776855</v>
+        <v>5.6196823120117188</v>
       </c>
     </row>
     <row r="10">
@@ -215,13 +215,13 @@
         <v>5.7543487548828125</v>
       </c>
       <c r="C10" s="2">
-        <v>5.6744871139526367</v>
+        <v>5.6745462417602539</v>
       </c>
       <c r="D10" s="2">
         <v>5.6649913787841797</v>
       </c>
       <c r="E10" s="2">
-        <v>5.5932760238647461</v>
+        <v>5.5919094085693359</v>
       </c>
     </row>
     <row r="11">
@@ -232,13 +232,13 @@
         <v>5.1833343505859375</v>
       </c>
       <c r="C11" s="2">
-        <v>5.1355934143066406</v>
+        <v>5.1394872665405273</v>
       </c>
       <c r="D11" s="2">
         <v>5.6486959457397461</v>
       </c>
       <c r="E11" s="2">
-        <v>5.5838813781738281</v>
+        <v>5.582430362701416</v>
       </c>
     </row>
     <row r="12">
@@ -249,13 +249,13 @@
         <v>5.4936356544494629</v>
       </c>
       <c r="C12" s="2">
-        <v>5.4596328735351562</v>
+        <v>5.4627857208251953</v>
       </c>
       <c r="D12" s="2">
         <v>5.6922369003295898</v>
       </c>
       <c r="E12" s="2">
-        <v>5.6361603736877441</v>
+        <v>5.6351108551025391</v>
       </c>
     </row>
     <row r="13">
@@ -266,13 +266,13 @@
         <v>6.305640697479248</v>
       </c>
       <c r="C13" s="2">
-        <v>6.2721972465515137</v>
+        <v>6.2750859260559082</v>
       </c>
       <c r="D13" s="2">
         <v>5.6948094367980957</v>
       </c>
       <c r="E13" s="2">
-        <v>5.640160083770752</v>
+        <v>5.6400198936462402</v>
       </c>
     </row>
     <row r="14">
@@ -283,13 +283,13 @@
         <v>5.4571723937988281</v>
       </c>
       <c r="C14" s="2">
-        <v>5.4075484275817871</v>
+        <v>5.4014849662780762</v>
       </c>
       <c r="D14" s="2">
         <v>5.8224291801452637</v>
       </c>
       <c r="E14" s="2">
-        <v>5.7810730934143066</v>
+        <v>5.7821793556213379</v>
       </c>
     </row>
     <row r="15">
@@ -300,13 +300,13 @@
         <v>5.9146013259887695</v>
       </c>
       <c r="C15" s="2">
-        <v>5.8810000419616699</v>
+        <v>5.8780803680419922</v>
       </c>
       <c r="D15" s="2">
         <v>5.8349251747131348</v>
       </c>
       <c r="E15" s="2">
-        <v>5.796140193939209</v>
+        <v>5.7971677780151367</v>
       </c>
     </row>
     <row r="16">
@@ -317,13 +317,13 @@
         <v>6.0408816337585449</v>
       </c>
       <c r="C16" s="2">
-        <v>6.0119681358337402</v>
+        <v>6.0132207870483398</v>
       </c>
       <c r="D16" s="2">
         <v>5.8363990783691406</v>
       </c>
       <c r="E16" s="2">
-        <v>5.7908806800842285</v>
+        <v>5.7909727096557617</v>
       </c>
     </row>
     <row r="17">
@@ -334,13 +334,13 @@
         <v>5.9996933937072754</v>
       </c>
       <c r="C17" s="2">
-        <v>5.953467845916748</v>
+        <v>5.9587564468383789</v>
       </c>
       <c r="D17" s="2">
         <v>5.7614188194274902</v>
       </c>
       <c r="E17" s="2">
-        <v>5.7143263816833496</v>
+        <v>5.7144031524658203</v>
       </c>
     </row>
     <row r="18">
@@ -351,13 +351,13 @@
         <v>6.2525529861450195</v>
       </c>
       <c r="C18" s="2">
-        <v>6.2337617874145508</v>
+        <v>6.2361674308776855</v>
       </c>
       <c r="D18" s="2">
         <v>5.6302089691162109</v>
       </c>
       <c r="E18" s="2">
-        <v>5.581913948059082</v>
+        <v>5.5815291404724121</v>
       </c>
     </row>
     <row r="19">
@@ -368,13 +368,13 @@
         <v>5.866814136505127</v>
       </c>
       <c r="C19" s="2">
-        <v>5.8100934028625488</v>
+        <v>5.8094396591186523</v>
       </c>
       <c r="D19" s="2">
         <v>5.6175198554992676</v>
       </c>
       <c r="E19" s="2">
-        <v>5.5591616630554199</v>
+        <v>5.557960033416748</v>
       </c>
     </row>
     <row r="20">
@@ -385,13 +385,13 @@
         <v>5.196601390838623</v>
       </c>
       <c r="C20" s="2">
-        <v>5.0882563591003418</v>
+        <v>5.0837316513061523</v>
       </c>
       <c r="D20" s="2">
         <v>5.5853214263916016</v>
       </c>
       <c r="E20" s="2">
-        <v>5.5207943916320801</v>
+        <v>5.5193872451782227</v>
       </c>
     </row>
     <row r="21">
@@ -402,13 +402,13 @@
         <v>4.818809986114502</v>
       </c>
       <c r="C21" s="2">
-        <v>4.7706451416015625</v>
+        <v>4.7736601829528809</v>
       </c>
       <c r="D21" s="2">
         <v>5.5110626220703125</v>
       </c>
       <c r="E21" s="2">
-        <v>5.4479928016662598</v>
+        <v>5.4470024108886719</v>
       </c>
     </row>
     <row r="22">
@@ -419,13 +419,13 @@
         <v>5.1247549057006836</v>
       </c>
       <c r="C22" s="2">
-        <v>5.0804829597473145</v>
+        <v>5.0792207717895508</v>
       </c>
       <c r="D22" s="2">
         <v>5.4660730361938477</v>
       </c>
       <c r="E22" s="2">
-        <v>5.400670051574707</v>
+        <v>5.399289608001709</v>
       </c>
     </row>
     <row r="23">
@@ -436,13 +436,13 @@
         <v>5.3429675102233887</v>
       </c>
       <c r="C23" s="2">
-        <v>5.2027802467346191</v>
+        <v>5.1893610954284668</v>
       </c>
       <c r="D23" s="2">
         <v>5.3781313896179199</v>
       </c>
       <c r="E23" s="2">
-        <v>5.2951059341430664</v>
+        <v>5.2924027442932129</v>
       </c>
     </row>
     <row r="24">
@@ -453,13 +453,13 @@
         <v>5.6248159408569336</v>
       </c>
       <c r="C24" s="2">
-        <v>5.5356922149658203</v>
+        <v>5.5309262275695801</v>
       </c>
       <c r="D24" s="2">
         <v>5.3765053749084473</v>
       </c>
       <c r="E24" s="2">
-        <v>5.2893743515014648</v>
+        <v>5.2862505912780762</v>
       </c>
     </row>
     <row r="25">
@@ -470,13 +470,13 @@
         <v>5.3725547790527344</v>
       </c>
       <c r="C25" s="2">
-        <v>5.3567571640014648</v>
+        <v>5.3617563247680664</v>
       </c>
       <c r="D25" s="2">
         <v>5.4768271446228027</v>
       </c>
       <c r="E25" s="2">
-        <v>5.394986629486084</v>
+        <v>5.3922820091247559</v>
       </c>
     </row>
     <row r="26">
@@ -487,13 +487,13 @@
         <v>5.5947842597961426</v>
       </c>
       <c r="C26" s="2">
-        <v>5.5275616645812988</v>
+        <v>5.5293416976928711</v>
       </c>
       <c r="D26" s="2">
         <v>5.6750822067260742</v>
       </c>
       <c r="E26" s="2">
-        <v>5.5882949829101562</v>
+        <v>5.5857424736022949</v>
       </c>
     </row>
     <row r="27">
@@ -504,13 +504,13 @@
         <v>5.4610805511474609</v>
       </c>
       <c r="C27" s="2">
-        <v>5.2836828231811523</v>
+        <v>5.2741856575012207</v>
       </c>
       <c r="D27" s="2">
         <v>5.7748432159423828</v>
       </c>
       <c r="E27" s="2">
-        <v>5.688011646270752</v>
+        <v>5.6860895156860352</v>
       </c>
     </row>
     <row r="28">
@@ -521,13 +521,13 @@
         <v>5.8521804809570312</v>
       </c>
       <c r="C28" s="2">
-        <v>5.758509635925293</v>
+        <v>5.7540721893310547</v>
       </c>
       <c r="D28" s="2">
         <v>5.861783504486084</v>
       </c>
       <c r="E28" s="2">
-        <v>5.781522274017334</v>
+        <v>5.7807402610778809</v>
       </c>
     </row>
     <row r="29">
@@ -538,13 +538,13 @@
         <v>6.0994977951049805</v>
       </c>
       <c r="C29" s="2">
-        <v>6.0387692451477051</v>
+        <v>6.0380158424377441</v>
       </c>
       <c r="D29" s="2">
         <v>5.9633522033691406</v>
       </c>
       <c r="E29" s="2">
-        <v>5.8913154602050781</v>
+        <v>5.891211986541748</v>
       </c>
     </row>
     <row r="30">
@@ -555,13 +555,13 @@
         <v>6.6031031608581543</v>
       </c>
       <c r="C30" s="2">
-        <v>6.5104174613952637</v>
+        <v>6.514803409576416</v>
       </c>
       <c r="D30" s="2">
         <v>6.1079134941101074</v>
       </c>
       <c r="E30" s="2">
-        <v>6.0332798957824707</v>
+        <v>6.0321674346923828</v>
       </c>
     </row>
     <row r="31">
@@ -572,13 +572,13 @@
         <v>6.0226054191589355</v>
       </c>
       <c r="C31" s="2">
-        <v>5.9779353141784668</v>
+        <v>5.9823436737060547</v>
       </c>
       <c r="D31" s="2">
         <v>6.231046199798584</v>
       </c>
       <c r="E31" s="2">
-        <v>6.1529388427734375</v>
+        <v>6.151465892791748</v>
       </c>
     </row>
     <row r="32">
@@ -589,13 +589,13 @@
         <v>6.1254277229309082</v>
       </c>
       <c r="C32" s="2">
-        <v>6.044374942779541</v>
+        <v>6.0412187576293945</v>
       </c>
       <c r="D32" s="2">
         <v>6.3293147087097168</v>
       </c>
       <c r="E32" s="2">
-        <v>6.266258716583252</v>
+        <v>6.2661452293395996</v>
       </c>
     </row>
     <row r="33">
@@ -606,13 +606,13 @@
         <v>6.5389351844787598</v>
       </c>
       <c r="C33" s="2">
-        <v>6.523831844329834</v>
+        <v>6.5251708030700684</v>
       </c>
       <c r="D33" s="2">
         <v>6.4010438919067383</v>
       </c>
       <c r="E33" s="2">
-        <v>6.3415679931640625</v>
+        <v>6.3420524597167969</v>
       </c>
     </row>
     <row r="34">
@@ -623,13 +623,13 @@
         <v>6.6736087799072266</v>
       </c>
       <c r="C34" s="2">
-        <v>6.6344366073608398</v>
+        <v>6.6303567886352539</v>
       </c>
       <c r="D34" s="2">
         <v>6.440340518951416</v>
       </c>
       <c r="E34" s="2">
-        <v>6.3831486701965332</v>
+        <v>6.3833169937133789</v>
       </c>
     </row>
     <row r="35">
@@ -640,13 +640,13 @@
         <v>6.7029752731323242</v>
       </c>
       <c r="C35" s="2">
-        <v>6.6044936180114746</v>
+        <v>6.6030268669128418</v>
       </c>
       <c r="D35" s="2">
         <v>6.4409151077270508</v>
       </c>
       <c r="E35" s="2">
-        <v>6.3860697746276855</v>
+        <v>6.3858590126037598</v>
       </c>
     </row>
     <row r="36">
@@ -657,13 +657,13 @@
         <v>6.3454971313476562</v>
       </c>
       <c r="C36" s="2">
-        <v>6.3035612106323242</v>
+        <v>6.3062987327575684</v>
       </c>
       <c r="D36" s="2">
         <v>6.5012750625610352</v>
       </c>
       <c r="E36" s="2">
-        <v>6.4491972923278809</v>
+        <v>6.4492177963256836</v>
       </c>
     </row>
     <row r="37">
@@ -674,13 +674,13 @@
         <v>6.497744083404541</v>
       </c>
       <c r="C37" s="2">
-        <v>6.4362921714782715</v>
+        <v>6.4372386932373047</v>
       </c>
       <c r="D37" s="2">
         <v>6.5255379676818848</v>
       </c>
       <c r="E37" s="2">
-        <v>6.4834651947021484</v>
+        <v>6.4846091270446777</v>
       </c>
     </row>
     <row r="38">
@@ -691,13 +691,13 @@
         <v>6.4531660079956055</v>
       </c>
       <c r="C38" s="2">
-        <v>6.4129962921142578</v>
+        <v>6.4093952178955078</v>
       </c>
       <c r="D38" s="2">
         <v>6.5302543640136719</v>
       </c>
       <c r="E38" s="2">
-        <v>6.4698481559753418</v>
+        <v>6.4706926345825195</v>
       </c>
     </row>
     <row r="39">
@@ -708,13 +708,13 @@
         <v>6.6082763671875</v>
       </c>
       <c r="C39" s="2">
-        <v>6.536707878112793</v>
+        <v>6.5376796722412109</v>
       </c>
       <c r="D39" s="2">
         <v>6.4985394477844238</v>
       </c>
       <c r="E39" s="2">
-        <v>6.4328503608703613</v>
+        <v>6.4340066909790039</v>
       </c>
     </row>
     <row r="40">
@@ -725,13 +725,13 @@
         <v>6.5658445358276367</v>
       </c>
       <c r="C40" s="2">
-        <v>6.5460801124572754</v>
+        <v>6.5525732040405273</v>
       </c>
       <c r="D40" s="2">
         <v>6.4407458305358887</v>
       </c>
       <c r="E40" s="2">
-        <v>6.3719758987426758</v>
+        <v>6.3729028701782227</v>
       </c>
     </row>
     <row r="41">
@@ -742,13 +742,13 @@
         <v>6.3437948226928711</v>
       </c>
       <c r="C41" s="2">
-        <v>6.3527865409851074</v>
+        <v>6.3597421646118164</v>
       </c>
       <c r="D41" s="2">
         <v>6.4252057075500488</v>
       </c>
       <c r="E41" s="2">
-        <v>6.3504338264465332</v>
+        <v>6.3507857322692871</v>
       </c>
     </row>
     <row r="42">
@@ -759,13 +759,13 @@
         <v>6.5813808441162109</v>
       </c>
       <c r="C42" s="2">
-        <v>6.4012770652770996</v>
+        <v>6.3999233245849609</v>
       </c>
       <c r="D42" s="2">
         <v>6.3403725624084473</v>
       </c>
       <c r="E42" s="2">
-        <v>6.2584586143493652</v>
+        <v>6.2584457397460938</v>
       </c>
     </row>
     <row r="43">
@@ -776,13 +776,13 @@
         <v>6.3881769180297852</v>
       </c>
       <c r="C43" s="2">
-        <v>6.3014569282531738</v>
+        <v>6.3001842498779297</v>
       </c>
       <c r="D43" s="2">
         <v>6.2758331298828125</v>
       </c>
       <c r="E43" s="2">
-        <v>6.1858644485473633</v>
+        <v>6.1856937408447266</v>
       </c>
     </row>
     <row r="44">
@@ -793,13 +793,13 @@
         <v>6.1828327178955078</v>
       </c>
       <c r="C44" s="2">
-        <v>6.0566267967224121</v>
+        <v>6.0530886650085449</v>
       </c>
       <c r="D44" s="2">
         <v>6.1890888214111328</v>
       </c>
       <c r="E44" s="2">
-        <v>6.0964183807373047</v>
+        <v>6.0953159332275391</v>
       </c>
     </row>
     <row r="45">
@@ -810,13 +810,13 @@
         <v>6.2056341171264648</v>
       </c>
       <c r="C45" s="2">
-        <v>6.1096820831298828</v>
+        <v>6.1072468757629395</v>
       </c>
       <c r="D45" s="2">
         <v>6.0504612922668457</v>
       </c>
       <c r="E45" s="2">
-        <v>5.9534921646118164</v>
+        <v>5.9511203765869141</v>
       </c>
     </row>
     <row r="46">
@@ -827,13 +827,13 @@
         <v>5.734245777130127</v>
       </c>
       <c r="C46" s="2">
-        <v>5.608515739440918</v>
+        <v>5.6061792373657227</v>
       </c>
       <c r="D46" s="2">
         <v>5.9565725326538086</v>
       </c>
       <c r="E46" s="2">
-        <v>5.8527154922485352</v>
+        <v>5.8488831520080566</v>
       </c>
     </row>
     <row r="47">
@@ -844,13 +844,13 @@
         <v>5.8723130226135254</v>
       </c>
       <c r="C47" s="2">
-        <v>5.759648323059082</v>
+        <v>5.7546267509460449</v>
       </c>
       <c r="D47" s="2">
         <v>5.8458490371704102</v>
       </c>
       <c r="E47" s="2">
-        <v>5.7476334571838379</v>
+        <v>5.7434148788452148</v>
       </c>
     </row>
     <row r="48">
@@ -861,13 +861,13 @@
         <v>5.8275761604309082</v>
       </c>
       <c r="C48" s="2">
-        <v>5.7316904067993164</v>
+        <v>5.7242789268493652</v>
       </c>
       <c r="D48" s="2">
         <v>5.7523899078369141</v>
       </c>
       <c r="E48" s="2">
-        <v>5.6532292366027832</v>
+        <v>5.6481728553771973</v>
       </c>
     </row>
     <row r="49">
@@ -878,13 +878,13 @@
         <v>5.3181986808776855</v>
       </c>
       <c r="C49" s="2">
-        <v>5.2597446441650391</v>
+        <v>5.2548127174377441</v>
       </c>
       <c r="D49" s="2">
         <v>5.7289185523986816</v>
       </c>
       <c r="E49" s="2">
-        <v>5.6242489814758301</v>
+        <v>5.6192169189453125</v>
       </c>
     </row>
     <row r="50">
@@ -895,13 +895,13 @@
         <v>5.4987936019897461</v>
       </c>
       <c r="C50" s="2">
-        <v>5.4457979202270508</v>
+        <v>5.4396076202392578</v>
       </c>
       <c r="D50" s="2">
         <v>5.6627049446105957</v>
       </c>
       <c r="E50" s="2">
-        <v>5.5500292778015137</v>
+        <v>5.5447492599487305</v>
       </c>
     </row>
     <row r="51">
@@ -912,13 +912,13 @@
         <v>5.5848722457885742</v>
       </c>
       <c r="C51" s="2">
-        <v>5.4555373191833496</v>
+        <v>5.450709342956543</v>
       </c>
       <c r="D51" s="2">
         <v>5.6605381965637207</v>
       </c>
       <c r="E51" s="2">
-        <v>5.5456857681274414</v>
+        <v>5.5397472381591797</v>
       </c>
     </row>
     <row r="52">
@@ -929,13 +929,13 @@
         <v>5.5470428466796875</v>
       </c>
       <c r="C52" s="2">
-        <v>5.4518184661865234</v>
+        <v>5.4430074691772461</v>
       </c>
       <c r="D52" s="2">
         <v>5.6019387245178223</v>
       </c>
       <c r="E52" s="2">
-        <v>5.4816675186157227</v>
+        <v>5.475466251373291</v>
       </c>
     </row>
     <row r="53">
@@ -946,13 +946,13 @@
         <v>5.9715890884399414</v>
       </c>
       <c r="C53" s="2">
-        <v>5.7958078384399414</v>
+        <v>5.7924838066101074</v>
       </c>
       <c r="D53" s="2">
         <v>5.529076099395752</v>
       </c>
       <c r="E53" s="2">
-        <v>5.3986625671386719</v>
+        <v>5.3926143646240234</v>
       </c>
     </row>
     <row r="54">
@@ -963,13 +963,13 @@
         <v>5.6097111701965332</v>
       </c>
       <c r="C54" s="2">
-        <v>5.4417014122009277</v>
+        <v>5.4370355606079102</v>
       </c>
       <c r="D54" s="2">
         <v>5.5129237174987793</v>
       </c>
       <c r="E54" s="2">
-        <v>5.3745760917663574</v>
+        <v>5.368462085723877</v>
       </c>
     </row>
     <row r="55">
@@ -980,13 +980,13 @@
         <v>5.714747428894043</v>
       </c>
       <c r="C55" s="2">
-        <v>5.569425106048584</v>
+        <v>5.5611639022827148</v>
       </c>
       <c r="D55" s="2">
         <v>5.4908051490783691</v>
       </c>
       <c r="E55" s="2">
-        <v>5.3444395065307617</v>
+        <v>5.3385248184204102</v>
       </c>
     </row>
     <row r="56">
@@ -997,13 +997,13 @@
         <v>5.3449158668518066</v>
       </c>
       <c r="C56" s="2">
-        <v>5.1834864616394043</v>
+        <v>5.1760964393615723</v>
       </c>
       <c r="D56" s="2">
         <v>5.4599113464355469</v>
       </c>
       <c r="E56" s="2">
-        <v>5.3135108947753906</v>
+        <v>5.3074569702148438</v>
       </c>
     </row>
     <row r="57">
@@ -1014,13 +1014,13 @@
         <v>5.1718158721923828</v>
       </c>
       <c r="C57" s="2">
-        <v>4.9846453666687012</v>
+        <v>4.9786128997802734</v>
       </c>
       <c r="D57" s="2">
         <v>5.4095525741577148</v>
       </c>
       <c r="E57" s="2">
-        <v>5.2712693214416504</v>
+        <v>5.2650165557861328</v>
       </c>
     </row>
     <row r="58">
@@ -1031,13 +1031,13 @@
         <v>5.1728272438049316</v>
       </c>
       <c r="C58" s="2">
-        <v>5.0429649353027344</v>
+        <v>5.0374417304992676</v>
       </c>
       <c r="D58" s="2">
         <v>5.3094196319580078</v>
       </c>
       <c r="E58" s="2">
-        <v>5.1814041137695312</v>
+        <v>5.1743407249450684</v>
       </c>
     </row>
     <row r="59">
@@ -1048,13 +1048,13 @@
         <v>5.2997260093688965</v>
       </c>
       <c r="C59" s="2">
-        <v>5.1745672225952148</v>
+        <v>5.1701736450195312</v>
       </c>
       <c r="D59" s="2">
         <v>5.3068537712097168</v>
       </c>
       <c r="E59" s="2">
-        <v>5.1773700714111328</v>
+        <v>5.1701788902282715</v>
       </c>
     </row>
     <row r="60">
@@ -1065,13 +1065,13 @@
         <v>5.3068251609802246</v>
       </c>
       <c r="C60" s="2">
-        <v>5.1771798133850098</v>
+        <v>5.1710977554321289</v>
       </c>
       <c r="D60" s="2">
         <v>5.2760229110717773</v>
       </c>
       <c r="E60" s="2">
-        <v>5.1442837715148926</v>
+        <v>5.136958122253418</v>
       </c>
     </row>
     <row r="61">
@@ -1082,13 +1082,13 @@
         <v>5.0938138961791992</v>
       </c>
       <c r="C61" s="2">
-        <v>5.0716452598571777</v>
+        <v>5.0610427856445312</v>
       </c>
       <c r="D61" s="2">
-        <v>5.2674112319946289</v>
+        <v>5.2907943725585938</v>
       </c>
       <c r="E61" s="2">
-        <v>5.1393833160400391</v>
+        <v>5.1585125923156738</v>
       </c>
     </row>
     <row r="62">
@@ -1099,13 +1099,13 @@
         <v>5.0703945159912109</v>
       </c>
       <c r="C62" s="2">
-        <v>4.9870219230651855</v>
+        <v>4.9764003753662109</v>
       </c>
       <c r="D62" s="2">
-        <v>5.2810678482055664</v>
+        <v>5.3137569427490234</v>
       </c>
       <c r="E62" s="2">
-        <v>5.1614885330200195</v>
+        <v>5.1887950897216797</v>
       </c>
     </row>
     <row r="63">
@@ -1116,13 +1116,13 @@
         <v>5.5866193771362305</v>
       </c>
       <c r="C63" s="2">
-        <v>5.4053940773010254</v>
+        <v>5.3995823860168457</v>
       </c>
       <c r="D63" s="2">
-        <v>5.299107551574707</v>
+        <v>5.3450398445129395</v>
       </c>
       <c r="E63" s="2">
-        <v>5.1812424659729004</v>
+        <v>5.2068648338317871</v>
       </c>
     </row>
     <row r="64">
@@ -1133,23 +1133,176 @@
         <v>5.4372677803039551</v>
       </c>
       <c r="C64" s="2">
-        <v>5.2716474533081055</v>
+        <v>5.2621755599975586</v>
       </c>
       <c r="D64" s="2">
-        <v>5.2989840507507324</v>
+        <v>5.3613033294677734</v>
       </c>
       <c r="E64" s="2">
-        <v>5.1825776100158691</v>
+        <v>5.2170267105102539</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="B65" s="2">
+        <v>5.4778590202331543</v>
+      </c>
+      <c r="C65" s="2">
+        <v>5.3700847625732422</v>
+      </c>
+      <c r="D65" s="2">
+        <v>5.3807101249694824</v>
+      </c>
+      <c r="E65" s="2">
+        <v>5.2341289520263672</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B66" s="2">
+        <v>5.3784780502319336</v>
+      </c>
+      <c r="C66" s="2">
+        <v>5.2511587142944336</v>
+      </c>
+      <c r="D66" s="2">
+        <v>5.3960580825805664</v>
+      </c>
+      <c r="E66" s="2">
+        <v>5.2410531044006348</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B67" s="2">
+        <v>5.4543757438659668</v>
+      </c>
+      <c r="C67" s="2">
+        <v>5.2000656127929688</v>
+      </c>
+      <c r="D67" s="2">
+        <v>5.4330883026123047</v>
+      </c>
+      <c r="E67" s="2">
+        <v>5.2681674957275391</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B68" s="2">
+        <v>5.4460959434509277</v>
+      </c>
+      <c r="C68" s="2">
+        <v>5.261631965637207</v>
+      </c>
+      <c r="D68" s="2">
+        <v>5.4014577865600586</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5.2367496490478516</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B69" s="2">
+        <v>5.4814858436584473</v>
+      </c>
+      <c r="C69" s="2">
+        <v>5.3250174522399902</v>
+      </c>
+      <c r="D69" s="2">
+        <v>5.38250732421875</v>
+      </c>
+      <c r="E69" s="2">
+        <v>5.2222037315368652</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B70" s="2">
+        <v>5.2319450378417969</v>
+      </c>
+      <c r="C70" s="2">
+        <v>5.1233615875244141</v>
+      </c>
+      <c r="D70" s="2">
+        <v>5.3705883026123047</v>
+      </c>
+      <c r="E70" s="2">
+        <v>5.2037186622619629</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B71" s="2">
+        <v>5.4036674499511719</v>
+      </c>
+      <c r="C71" s="2">
+        <v>5.220430850982666</v>
+      </c>
+      <c r="D71" s="2">
+        <v>5.3694610595703125</v>
+      </c>
+      <c r="E71" s="2">
+        <v>5.1969418525695801</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B72" s="2">
+        <v>5.301945686340332</v>
+      </c>
+      <c r="C72" s="2">
+        <v>5.1168198585510254</v>
+      </c>
+      <c r="D72" s="2">
+        <v>5.3553085327148438</v>
+      </c>
+      <c r="E72" s="2">
+        <v>5.1964211463928223</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B73" s="2">
+        <v>5.2667117118835449</v>
+      </c>
+      <c r="C73" s="2">
+        <v>5.1312642097473145</v>
+      </c>
+      <c r="D73" s="2">
+        <v>5.337151050567627</v>
+      </c>
+      <c r="E73" s="2">
+        <v>5.1833786964416504</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
     </row>
   </sheetData>
 </worksheet>
